--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,10 +432,22 @@
           <t>equip_kind</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>battle_usable</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>battle_heal_hp</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>battle_heal_mp</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
@@ -447,6 +459,21 @@
           <t>装备部位:0=不是装备。&gt;0=该部位编号。部位的含义(手镯/头/胸…)以及每个部位有几个槽,全部由数据定义 —— 槽位表 EquipSlot 决定哪个槽接受哪个部位,代码里不写死</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>回合制战斗内可用:0=不可用,1=可用</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>战斗内使用回复的生命值(0=不回血)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>战斗内使用回复的法力值(0=不回蓝)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -457,6 +484,15 @@
       </c>
       <c r="C6" t="n">
         <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -469,6 +505,15 @@
       <c r="C7" t="n">
         <v>1</v>
       </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -480,6 +525,15 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -491,6 +545,15 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -502,6 +565,15 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -513,6 +585,15 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -524,6 +605,15 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -535,6 +625,15 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -546,6 +645,15 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -557,6 +665,15 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>300</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -568,6 +685,15 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -579,6 +705,15 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -590,6 +725,15 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -601,6 +745,15 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -612,6 +765,15 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -623,6 +785,15 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -634,6 +805,15 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +825,15 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -656,6 +845,15 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -667,6 +865,15 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -678,6 +885,15 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -689,6 +905,15 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -700,6 +925,15 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -711,6 +945,15 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -722,6 +965,15 @@
       <c r="C30" t="n">
         <v>0</v>
       </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -733,6 +985,15 @@
       <c r="C31" t="n">
         <v>0</v>
       </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -744,6 +1005,15 @@
       <c r="C32" t="n">
         <v>0</v>
       </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -753,6 +1023,15 @@
         <v>999</v>
       </c>
       <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,50 @@
           <t>battle_heal_mp</t>
         </is>
       </c>
-    </row>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>icon_key</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>equip_level</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>equip_class</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>affix_pool</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>base_attr</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>affix_rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
@@ -472,6 +515,46 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>战斗内使用回复的法力值(0=不回蓝)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>物品名(下发客户端)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>描述(下发客户端 tooltip)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>图标 Resources 路径(UI/ 开头,不带扩展名);空 = 客户端兜底图标</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>佩戴等级,同时是查属性上限(EquipAttributeCap)用的装备等级</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>职业要求(Class.id);0 = 不限</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>随机属性池(EquipAffixPool.pool_id,不是那张表的主键,所以不设外键);0 = 不掷</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>基础属性:每槽 (EquipAttribute.id, 数值),最多 3 条;用不到的槽留空,不要填 0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>掷值规则。FK -&gt; EquipAffixRule.id;0 = 不掷</t>
         </is>
       </c>
     </row>
@@ -1033,6 +1116,1021 @@
       </c>
       <c r="F33" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>新手木剑</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1级武器,提供伤害。</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/012_peachwood_sword</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>40</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>青锋剑</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>20级武器,提供伤害。</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/007_flying_sword</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>420</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>寒铁剑</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>40级武器,提供伤害。</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/001_daoist_saber</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>40</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>820</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>流云剑</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>60级武器,提供伤害。</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/074_lu_dongbin_immortal_sword</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>60</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1220</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>11</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>惊雷剑</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>80级武器,提供伤害。</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/19_lu_dongbin_immortal_sword</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>80</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1620</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>布头巾</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1级帽子,提供防御。</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>12</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>青纱冠</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>20级帽子,提供防御。</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>20</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>126</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>寒铁盔</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>40级帽子,提供防御。</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>40</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8</v>
+      </c>
+      <c r="N41" t="n">
+        <v>246</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>流云冠</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>60级帽子,提供防御。</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>60</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>8</v>
+      </c>
+      <c r="N42" t="n">
+        <v>366</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>惊雷冠</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>80级帽子,提供防御。</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>80</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>8</v>
+      </c>
+      <c r="N43" t="n">
+        <v>486</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>粗布衣</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1级衣服,提供防御。</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>8</v>
+      </c>
+      <c r="N44" t="n">
+        <v>24</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>13</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>青纱袍</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>20级衣服,提供防御。</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>20</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>252</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>13</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>寒铁甲</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>40级衣服,提供防御。</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>40</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>8</v>
+      </c>
+      <c r="N46" t="n">
+        <v>492</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>13</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>流云袍</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>60级衣服,提供防御。</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>60</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>8</v>
+      </c>
+      <c r="N47" t="n">
+        <v>732</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>惊雷甲</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>80级衣服,提供防御。</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>80</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>8</v>
+      </c>
+      <c r="N48" t="n">
+        <v>972</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>14</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>草鞋</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1级鞋子,提供防御与速度。</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N49" t="n">
+        <v>12</v>
+      </c>
+      <c r="O49" t="n">
+        <v>11</v>
+      </c>
+      <c r="P49" t="n">
+        <v>12</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>青纱履</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>20级鞋子,提供防御与速度。</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>126</v>
+      </c>
+      <c r="O50" t="n">
+        <v>11</v>
+      </c>
+      <c r="P50" t="n">
+        <v>88</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>14</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>寒铁靴</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>40级鞋子,提供防御与速度。</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>40</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>246</v>
+      </c>
+      <c r="O51" t="n">
+        <v>11</v>
+      </c>
+      <c r="P51" t="n">
+        <v>168</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>14</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>流云履</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>60级鞋子,提供防御与速度。</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>60</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" t="n">
+        <v>366</v>
+      </c>
+      <c r="O52" t="n">
+        <v>11</v>
+      </c>
+      <c r="P52" t="n">
+        <v>248</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>14</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>惊雷靴</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>80级鞋子,提供防御与速度。</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>80</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>8</v>
+      </c>
+      <c r="N53" t="n">
+        <v>486</v>
+      </c>
+      <c r="O53" t="n">
+        <v>11</v>
+      </c>
+      <c r="P53" t="n">
+        <v>328</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2445,6 +2445,886 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67">
+        <v>1110</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>11</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>青铜剑</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>10级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/012_peachwood_sword</t>
+        </is>
+      </c>
+      <c r="J67">
+        <v>10</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>220</v>
+      </c>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+      <c r="R67"/>
+      <c r="S67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>1130</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>11</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>玄铁剑</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>30级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/007_flying_sword</t>
+        </is>
+      </c>
+      <c r="J68">
+        <v>30</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>620</v>
+      </c>
+      <c r="O68"/>
+      <c r="P68"/>
+      <c r="Q68"/>
+      <c r="R68"/>
+      <c r="S68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>1150</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>11</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>龙纹剑</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>50级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/001_daoist_saber</t>
+        </is>
+      </c>
+      <c r="J69">
+        <v>50</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <v>1020</v>
+      </c>
+      <c r="O69"/>
+      <c r="P69"/>
+      <c r="Q69"/>
+      <c r="R69"/>
+      <c r="S69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>1170</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>11</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>星陨剑</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>70级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>UI/qdao_v3/icons_weapon/074_lu_dongbin_immortal_sword</t>
+        </is>
+      </c>
+      <c r="J70">
+        <v>70</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>1420</v>
+      </c>
+      <c r="O70"/>
+      <c r="P70"/>
+      <c r="Q70"/>
+      <c r="R70"/>
+      <c r="S70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>1210</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>12</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>青纹冠</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>10级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I71"/>
+      <c r="J71">
+        <v>10</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>2</v>
+      </c>
+      <c r="M71">
+        <v>8</v>
+      </c>
+      <c r="N71">
+        <v>66</v>
+      </c>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+      <c r="R71"/>
+      <c r="S71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>1230</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>12</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>玄铁盔</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>30级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I72"/>
+      <c r="J72">
+        <v>30</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+      <c r="M72">
+        <v>8</v>
+      </c>
+      <c r="N72">
+        <v>186</v>
+      </c>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>1250</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>12</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>龙纹盔</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>50级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I73"/>
+      <c r="J73">
+        <v>50</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>2</v>
+      </c>
+      <c r="M73">
+        <v>8</v>
+      </c>
+      <c r="N73">
+        <v>306</v>
+      </c>
+      <c r="O73"/>
+      <c r="P73"/>
+      <c r="Q73"/>
+      <c r="R73"/>
+      <c r="S73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>1270</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>12</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>星陨冠</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>70级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I74"/>
+      <c r="J74">
+        <v>70</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+      <c r="M74">
+        <v>8</v>
+      </c>
+      <c r="N74">
+        <v>426</v>
+      </c>
+      <c r="O74"/>
+      <c r="P74"/>
+      <c r="Q74"/>
+      <c r="R74"/>
+      <c r="S74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>1310</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>13</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>青纹袍</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I75"/>
+      <c r="J75">
+        <v>10</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>2</v>
+      </c>
+      <c r="M75">
+        <v>8</v>
+      </c>
+      <c r="N75">
+        <v>132</v>
+      </c>
+      <c r="O75"/>
+      <c r="P75"/>
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="S75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>1330</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>13</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>玄铁甲</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>30级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I76"/>
+      <c r="J76">
+        <v>30</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>2</v>
+      </c>
+      <c r="M76">
+        <v>8</v>
+      </c>
+      <c r="N76">
+        <v>372</v>
+      </c>
+      <c r="O76"/>
+      <c r="P76"/>
+      <c r="Q76"/>
+      <c r="R76"/>
+      <c r="S76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>1350</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>13</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>龙纹甲</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>50级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I77"/>
+      <c r="J77">
+        <v>50</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>8</v>
+      </c>
+      <c r="N77">
+        <v>612</v>
+      </c>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="S77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>1370</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>13</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>星陨袍</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>70级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I78"/>
+      <c r="J78">
+        <v>70</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>8</v>
+      </c>
+      <c r="N78">
+        <v>852</v>
+      </c>
+      <c r="O78"/>
+      <c r="P78"/>
+      <c r="Q78"/>
+      <c r="R78"/>
+      <c r="S78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>1410</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <v>14</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>青纹靴</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>10级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I79"/>
+      <c r="J79">
+        <v>10</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>2</v>
+      </c>
+      <c r="M79">
+        <v>8</v>
+      </c>
+      <c r="N79">
+        <v>66</v>
+      </c>
+      <c r="O79">
+        <v>11</v>
+      </c>
+      <c r="P79">
+        <v>48</v>
+      </c>
+      <c r="Q79"/>
+      <c r="R79"/>
+      <c r="S79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>1430</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>14</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>玄铁靴</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>30级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I80"/>
+      <c r="J80">
+        <v>30</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>8</v>
+      </c>
+      <c r="N80">
+        <v>186</v>
+      </c>
+      <c r="O80">
+        <v>11</v>
+      </c>
+      <c r="P80">
+        <v>128</v>
+      </c>
+      <c r="Q80"/>
+      <c r="R80"/>
+      <c r="S80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>1450</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>14</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>龙纹靴</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>50级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I81"/>
+      <c r="J81">
+        <v>50</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>8</v>
+      </c>
+      <c r="N81">
+        <v>306</v>
+      </c>
+      <c r="O81">
+        <v>11</v>
+      </c>
+      <c r="P81">
+        <v>208</v>
+      </c>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>1470</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>14</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>星陨靴</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>70级装备，提供本部位基础属性。</t>
+        </is>
+      </c>
+      <c r="I82"/>
+      <c r="J82">
+        <v>70</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>2</v>
+      </c>
+      <c r="M82">
+        <v>8</v>
+      </c>
+      <c r="N82">
+        <v>426</v>
+      </c>
+      <c r="O82">
+        <v>11</v>
+      </c>
+      <c r="P82">
+        <v>288</v>
+      </c>
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="S82">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
